--- a/resources/templates/standard/L1100-12.xlsx
+++ b/resources/templates/standard/L1100-12.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>NO</t>
   </si>
@@ -736,7 +739,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -800,22 +805,22 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -823,7 +828,7 @@
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1311,19 +1316,19 @@
       <c r="M27" s="29"/>
       <c r="N27" s="29"/>
       <c r="O27" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P27" s="31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q27" s="31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R27" s="31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S27" s="31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
